--- a/Zeitplan.xlsx
+++ b/Zeitplan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c31e1f75d70dd27/Dokumente/Viktor/Uni/Module/Hauptseminar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c31e1f75d70dd27/Dokumente/Viktor/Uni/Module/Hauptseminar/HS Projekt/hsar1-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{DEB8F74F-79D1-44B4-A6E6-07C1AB08969D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49E96A71-9905-4D02-BAB6-6F942D847418}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{DEB8F74F-79D1-44B4-A6E6-07C1AB08969D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F8BEAE9-7342-4300-B46E-6794A101A60C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{160B5B28-2411-4C44-ADB3-AEA1509A83E1}"/>
   </bookViews>
@@ -118,9 +118,6 @@
     <t>Zustandsmaschinen erstellen</t>
   </si>
   <si>
-    <t>Pfadvorgabengenerator</t>
-  </si>
-  <si>
     <t>Parklückendetektion</t>
   </si>
   <si>
@@ -167,6 +164,9 @@
   </si>
   <si>
     <t>Dokumentation</t>
+  </si>
+  <si>
+    <t>Pfadvorgabengenerator entwerfen</t>
   </si>
 </sst>
 </file>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="13" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A13" s="19" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>15</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="15" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A15" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>18</v>
@@ -2527,7 +2527,7 @@
     </row>
     <row r="17" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A17" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>20</v>
@@ -2672,10 +2672,10 @@
     </row>
     <row r="18" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A18" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" s="16">
         <v>0</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="19" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A19" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="16">
         <v>0</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="20" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A20" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>25</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>26</v>
       </c>
       <c r="C20" s="16">
         <v>0</v>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="21" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A21" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" s="16">
         <v>0</v>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="22" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A22" s="19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C22" s="16">
         <v>0</v>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="23" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A23" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" s="16">
         <v>0</v>
@@ -3541,10 +3541,10 @@
     </row>
     <row r="24" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A24" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="17">
@@ -3832,7 +3832,7 @@
     </row>
     <row r="26" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A26" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="22" t="s">
         <v>15</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="27" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A27" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>15</v>
@@ -4307,10 +4307,10 @@
     </row>
     <row r="29" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A29" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="23">
         <v>0</v>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="30" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A30" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C30" s="23"/>
       <c r="D30" s="24">
@@ -4561,10 +4561,10 @@
     </row>
     <row r="31" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A31" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31" s="23">
         <v>0</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="32" spans="1:41" ht="24" customHeight="1" thickBot="1">
       <c r="A32" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="23"/>
       <c r="D32" s="24">
